--- a/artfynd/A 20073-2019 artfynd.xlsx
+++ b/artfynd/A 20073-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -900,6 +900,455 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>115049409</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57388</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>V Toresbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>547255</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6282930</v>
+      </c>
+      <c r="S4" t="n">
+        <v>150</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Örsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Emil Lundahl</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Emil Lundahl</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>115049405</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57245</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>V Toresbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>547255</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6282930</v>
+      </c>
+      <c r="S5" t="n">
+        <v>150</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Örsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Emil Lundahl</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Emil Lundahl</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>115049407</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57258</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>V Toresbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>547255</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6282930</v>
+      </c>
+      <c r="S6" t="n">
+        <v>150</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Örsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Emil Lundahl</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Emil Lundahl</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>115049412</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57860</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102124</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vinterhämpling</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Linaria flavirostris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>sträckande</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>V Toresbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>547255</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6282930</v>
+      </c>
+      <c r="S7" t="n">
+        <v>150</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Örsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Emil Lundahl</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Emil Lundahl</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
